--- a/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultipletables.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultipletables.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce1a7f8dbeaa4c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb4f82d15012441d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -165,8 +165,8 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b8059fd30d64c37"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe6f2cd1ef754029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4718125954a74bb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5731f9908e664d27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultipletables.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultipletables.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb4f82d15012441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R156ea891269b4eae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -165,8 +165,8 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4718125954a74bb6"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5731f9908e664d27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bea1236da854a4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a341deabed844f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultipletables.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testgetattributeasjsonmultipletables.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R156ea891269b4eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R083a7deae20b40a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -165,8 +165,8 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bea1236da854a4b"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a341deabed844f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd65b32c3e1114ce1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64d0e33248484444"/>
   </x:tableParts>
 </x:worksheet>
 </file>